--- a/Atlas/Hum/AAL_dictionary.xlsx
+++ b/Atlas/Hum/AAL_dictionary.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\dog_brain_toolkit\Atlas\Hum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F98FEC48-FF90-4B5D-BCA1-48501F6E9CE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC0562FF-BE71-46BE-8546-A67D926BB809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3465" windowWidth="21600" windowHeight="11295"/>
+    <workbookView xWindow="14430" yWindow="1935" windowWidth="14790" windowHeight="13485" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AAL_dictionary" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="198">
   <si>
     <t>Number</t>
   </si>
@@ -611,12 +611,15 @@
   </si>
   <si>
     <t>Raphe_M</t>
+  </si>
+  <si>
+    <t>Description</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1450,11 +1453,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C171"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D171"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="26.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1464,8 +1470,11 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1473,7 +1482,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1481,7 +1490,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1489,7 +1498,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1497,7 +1506,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1505,7 +1514,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1513,7 +1522,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1524,7 +1533,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1535,7 +1544,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1546,7 +1555,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1557,7 +1566,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1565,7 +1574,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1573,7 +1582,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1581,7 +1590,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1589,7 +1598,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
